--- a/NewShopEntry/Pampanikal/2080/8_Magh2080.xlsx
+++ b/NewShopEntry/Pampanikal/2080/8_Magh2080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\shop-main\NewShopEntry\Pampanikal\2080\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5531166-C9D4-478A-B29E-2A9DC61F0E0C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCAE709A-0F2D-47C6-AFA0-C30403BE2129}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{B3429875-737F-40AC-B95F-7B26A6BBCF55}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="17">
   <si>
     <t>Pampanikal</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>REMAINING</t>
+  </si>
+  <si>
+    <t>01/15/2081Paid</t>
   </si>
 </sst>
 </file>
@@ -195,12 +198,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="16" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -215,11 +218,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -664,7 +667,7 @@
         <v>580</v>
       </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="7"/>
+      <c r="D11" s="6"/>
       <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
@@ -686,7 +689,7 @@
         <v>400</v>
       </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="7"/>
+      <c r="D13" s="6"/>
       <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
@@ -697,14 +700,14 @@
         <v>175</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="7"/>
+      <c r="D14" s="6"/>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A15" s="7"/>
+      <c r="A15" s="6"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="7"/>
+      <c r="D15" s="6"/>
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
@@ -731,7 +734,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12"/>
-      <c r="C18" s="7"/>
+      <c r="C18" s="6"/>
       <c r="D18" s="13">
         <f>15000-6085</f>
         <v>8915</v>
@@ -739,23 +742,27 @@
       <c r="E18" s="13"/>
     </row>
     <row r="19" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="16">
+      <c r="B19" s="8"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="9">
         <f>B17-D18</f>
         <v>1780</v>
       </c>
-      <c r="E19" s="16"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="E19" s="9"/>
+    </row>
+    <row r="20" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+      <c r="A20" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="14"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="16">
+        <v>1780</v>
+      </c>
+      <c r="E20" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="9">
